--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487542_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487542_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4509</v>
+        <v>6.0266</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6878</v>
+        <v>4.1565</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7631</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="n">
         <v>4.5545</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0828</v>
+        <v>0.4929</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1782</v>
+        <v>0.2905</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0954</v>
+        <v>0.2023</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0648</v>
+        <v>5.909</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0924</v>
+        <v>3.4821</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9725</v>
+        <v>2.4269</v>
       </c>
       <c r="G3" t="n">
         <v>2.0564</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6379</v>
+        <v>0.2063</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2298</v>
+        <v>0.16</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4081</v>
+        <v>0.0463</v>
       </c>
       <c r="V3" t="n">
         <v>1.492</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>I. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.378</v>
+        <v>3.9323</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1615</v>
+        <v>1.6587</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5395</v>
+        <v>2.2736</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0982</v>
+        <v>1.6133</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0122</v>
+        <v>0.3708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.914</v>
+        <v>1.2425</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4247</v>
+        <v>1.1842</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2008</v>
+        <v>-0.0427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.2269</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5229</v>
+        <v>0.4291</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8114</v>
+        <v>0.4135</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2885</v>
+        <v>0.0156</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8703</v>
+        <v>0.4768</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3723</v>
+        <v>-0.0382</v>
       </c>
       <c r="U4" t="n">
-        <v>1.498</v>
+        <v>0.5151</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9977</v>
+        <v>0.2754</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X4" t="n">
-        <v>1.9977</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. GRANJA I BERNAD</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2842</v>
+        <v>3.2906</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8236</v>
+        <v>0.699</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4607</v>
+        <v>2.5916</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6133</v>
+        <v>1.3421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3708</v>
+        <v>0.8212</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2425</v>
+        <v>0.5209</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1842</v>
+        <v>1.5162</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0427</v>
+        <v>0.7483</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2269</v>
+        <v>0.7679</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4291</v>
+        <v>-0.174</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4135</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0156</v>
+        <v>-0.2469</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1712</v>
+        <v>0.6903</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8734</v>
+        <v>0.1159</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7022</v>
+        <v>0.5745</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2754</v>
+        <v>2.4332</v>
       </c>
       <c r="W5" t="n">
-        <v>1.492</v>
+        <v>2.9839</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0519</v>
+        <v>2.9622</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2732</v>
+        <v>-1.0427</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7787</v>
+        <v>4.0049</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3421</v>
+        <v>-0.0982</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8212</v>
+        <v>-1.0122</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5209</v>
+        <v>0.914</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5162</v>
+        <v>0.4247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7483</v>
+        <v>-0.2008</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7679</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.174</v>
+        <v>-0.5229</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.8114</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2469</v>
+        <v>0.2885</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4516</v>
+        <v>1.4545</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.31</v>
+        <v>0.4911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.9634</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4332</v>
+        <v>1.9977</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9839</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5507</v>
+        <v>1.9977</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9103</v>
+        <v>1.2566</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4292</v>
+        <v>0.5082</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4811</v>
+        <v>0.7484</v>
       </c>
       <c r="G7" t="n">
         <v>0.4725</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3998</v>
+        <v>0.746</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7673</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3676</v>
+        <v>-0.1003</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9412</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8969</v>
+        <v>0.89</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1767</v>
+        <v>1.1698</v>
       </c>
       <c r="F8" t="n">
         <v>-0.2798</v>
@@ -1078,10 +1078,10 @@
         <v>2.546</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8926</v>
+        <v>0.8857</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8973</v>
+        <v>0.8904</v>
       </c>
       <c r="U8" t="n">
         <v>-0.0047</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2562</v>
+        <v>-0.1968</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3373</v>
+        <v>0.2303</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3581</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3442</v>
+        <v>-0.3917</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.297</v>
+        <v>-0.2376</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0472</v>
+        <v>-0.1541</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7381</v>
+        <v>-0.5985</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1513</v>
+        <v>-1.0919</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4132</v>
+        <v>0.4934</v>
       </c>
       <c r="G10" t="n">
         <v>-1.652</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1305</v>
+        <v>0.2701</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0306</v>
+        <v>0.0288</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1611</v>
+        <v>0.2413</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. NGUFOR</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1633</v>
+        <v>-2.0354</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3778</v>
+        <v>-1.6674</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7855</v>
+        <v>-0.368</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3252</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1298</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4549</v>
+        <v>-0.1361</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0064</v>
+        <v>0.2029</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2529</v>
+        <v>0.1212</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6812</v>
+        <v>-0.8677</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8833</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.2573</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.3294</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6671</v>
+        <v>0.0798</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5121</v>
+        <v>0.0882</v>
       </c>
       <c r="U12" t="n">
-        <v>0.155</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>J. NGUFOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3354</v>
+        <v>-2.8945</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7268</v>
+        <v>-1.9753</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6086</v>
+        <v>-0.9191</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6647999999999999</v>
+        <v>0.3252</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.1298</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1361</v>
+        <v>0.4549</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2029</v>
+        <v>2.0064</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1212</v>
+        <v>1.2529</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8677</v>
+        <v>-1.6812</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.8833</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2573</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1751</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2201</v>
+        <v>0.9359</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0288</v>
+        <v>0.9145</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.249</v>
+        <v>0.0213</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.9518</v>
+        <v>17.843</v>
       </c>
       <c r="E14" t="n">
-        <v>4.088100000000002</v>
+        <v>4.978999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>12.8639</v>
@@ -1525,7 +1525,7 @@
         <v>0.9687999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>9.3177</v>
+        <v>9.317700000000002</v>
       </c>
       <c r="M14" t="n">
         <v>-3.8701</v>
@@ -1537,7 +1537,7 @@
         <v>-1.865</v>
       </c>
       <c r="P14" t="n">
-        <v>3.916800000000001</v>
+        <v>3.9168</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.7094</v>
@@ -1546,10 +1546,10 @@
         <v>17.6262</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8963</v>
+        <v>5.7872</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5994</v>
+        <v>3.4905</v>
       </c>
       <c r="U14" t="n">
         <v>2.2967</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3649</v>
+        <v>2.5684</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2472</v>
+        <v>1.5308</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1177</v>
+        <v>1.0375</v>
       </c>
       <c r="G15" t="n">
         <v>1.988</v>
@@ -1624,13 +1624,13 @@
         <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5727</v>
+        <v>0.7762</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2457</v>
+        <v>0.5293</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3271</v>
+        <v>0.2469</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9368</v>
+        <v>2.3698</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9169</v>
+        <v>1.5076</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0199</v>
+        <v>0.8623</v>
       </c>
       <c r="G16" t="n">
         <v>2.2335</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0449</v>
+        <v>0.478</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5681</v>
+        <v>0.1588</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4768</v>
+        <v>0.3192</v>
       </c>
       <c r="V16" t="n">
         <v>0.05</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.279</v>
+        <v>1.0191</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0853</v>
+        <v>0.983</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1937</v>
+        <v>0.0361</v>
       </c>
       <c r="G17" t="n">
         <v>-0.007900000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4866</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4705</v>
+        <v>-0.5729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.016</v>
+        <v>-0.1736</v>
       </c>
       <c r="V17" t="n">
         <v>1.3818</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BLANCO CARBALLO</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3908</v>
+        <v>0.3614</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3326</v>
+        <v>1.2201</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0582</v>
+        <v>-0.8586</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5112</v>
+        <v>0.2761</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1354</v>
+        <v>-0.8199</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6466</v>
+        <v>1.096</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6466</v>
+        <v>1.0094</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.2127</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6466</v>
+        <v>1.2221</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1354</v>
+        <v>-0.7333</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1354</v>
+        <v>-0.6073</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.1261</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0772</v>
+        <v>-0.2151</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0772</v>
+        <v>-0.1504</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.8747</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>R. BLANCO CARBALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5808</v>
+        <v>-0.3641</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7084</v>
+        <v>-0.3326</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2891</v>
+        <v>-0.0315</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2761</v>
+        <v>0.5112</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8199</v>
+        <v>-0.1354</v>
       </c>
       <c r="I19" t="n">
-        <v>1.096</v>
+        <v>0.6466</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0094</v>
+        <v>0.6466</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2127</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2221</v>
+        <v>0.6466</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7333</v>
+        <v>-0.1354</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6073</v>
+        <v>-0.1354</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1261</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1573</v>
+        <v>0.104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5764</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5809</v>
+        <v>0.104</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8747</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2457</v>
+        <v>-1.8806</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9115</v>
+        <v>-1.7069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341</v>
+        <v>-0.1738</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1372</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3234</v>
+        <v>-0.9584</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5346</v>
+        <v>-0.3299</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.6284</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1767</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2531</v>
+        <v>-2.1968</v>
       </c>
       <c r="E21" t="n">
         <v>-3.2571</v>
       </c>
       <c r="F21" t="n">
-        <v>1.004</v>
+        <v>1.0603</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7957</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1899</v>
+        <v>-0.1337</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2153</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0254</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>1.3408</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>A. BARRIOS UREÑA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0467</v>
+        <v>-2.5541</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1122</v>
+        <v>-2.2866</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9345</v>
+        <v>-0.2675</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4417</v>
+        <v>1.0593</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0987</v>
+        <v>-0.5577</v>
       </c>
       <c r="I22" t="n">
-        <v>0.657</v>
+        <v>1.617</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.298</v>
+        <v>1.9291</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9446</v>
+        <v>0.5954</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6466</v>
+        <v>1.3337</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1437</v>
+        <v>-0.8698</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1541</v>
+        <v>-1.153</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0104</v>
+        <v>0.2833</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7834</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1784</v>
+        <v>-0.6959</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0723</v>
+        <v>-0.1835</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2507</v>
+        <v>-0.5124</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.5673</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>-0.1152</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>-0.4521</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BARRIOS UREÑA</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1994</v>
+        <v>-3.8616</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7983</v>
+        <v>-2.4192</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4011</v>
+        <v>-1.4424</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0593</v>
+        <v>-2.4417</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5577</v>
+        <v>-3.0987</v>
       </c>
       <c r="I23" t="n">
-        <v>1.617</v>
+        <v>0.657</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9291</v>
+        <v>-1.298</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5954</v>
+        <v>-1.9446</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3337</v>
+        <v>0.6466</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8698</v>
+        <v>-1.1437</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.153</v>
+        <v>-1.1541</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2833</v>
+        <v>0.0104</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3502</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3412</v>
+        <v>-0.6365</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6952</v>
+        <v>-0.3794</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6461</v>
+        <v>-0.2572</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5673</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1152</v>
+        <v>1.2166</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4521</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1578</v>
+        <v>-3.9394</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0907</v>
+        <v>-3.1931</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0671</v>
+        <v>-0.7463</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5871</v>
@@ -2326,13 +2326,13 @@
         <v>1.5668</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0689</v>
+        <v>-0.8504</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4111</v>
+        <v>-0.5134</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.337</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1101</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.658300000000001</v>
+        <v>-7.7918</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3192</v>
+        <v>-4.9099</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3391</v>
+        <v>-2.8819</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5149</v>
@@ -2404,13 +2404,13 @@
         <v>1.7626</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2022</v>
+        <v>-1.3357</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1351</v>
+        <v>-0.7258</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0671</v>
+        <v>-0.6099</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7662</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.9519</v>
+        <v>-16.2697</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.8638</v>
+        <v>-12.8639</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.0879</v>
+        <v>-3.4058</v>
       </c>
       <c r="G26" t="n">
         <v>-6.416399999999999</v>
@@ -2467,7 +2467,7 @@
         <v>-10.2863</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9688000000000001</v>
+        <v>-0.9687999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-9.317599999999999</v>
@@ -2482,13 +2482,13 @@
         <v>13.7093</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.8963</v>
+        <v>-4.214</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.2967</v>
+        <v>-2.2968</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.5995</v>
+        <v>-1.9172</v>
       </c>
       <c r="V26" t="n">
         <v>-1.7224</v>
